--- a/examples/acme-corp/leave_calendar.xlsx
+++ b/examples/acme-corp/leave_calendar.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отсутствия" sheetId="1" r:id="R31b2ee145d9b4625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="2" r:id="Rf6708abcd2b341e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отсутствия" sheetId="1" r:id="Rb159c346dd5e4963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="2" r:id="R6ba5004514b94e52"/>
   </x:sheets>
 </x:workbook>
 </file>
